--- a/ZonasEscolares/excels/LORETO-MAYNAS-BELEN.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-BELEN.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LORETO-MAYNAS-BELEN.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-BELEN.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>61006 SARA ALICIA SABERBEIN PINEDO</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-3.76143</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-73.24947</v>
-      </c>
-      <c r="I2" t="n">
-        <v>518</v>
-      </c>
-      <c r="J2" t="n">
-        <v>29</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-3.76143</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-73.24947</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>159 NIÑO DE JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-3.75938</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-73.25171</v>
-      </c>
-      <c r="I3" t="n">
-        <v>415</v>
-      </c>
-      <c r="J3" t="n">
-        <v>19</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-3.75938</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-73.25171</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>178 LILY VASQUEZ RIBEIRO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-3.76196</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-73.25252999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>387</v>
-      </c>
-      <c r="J4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-3.76196</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-73.25253</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>397 CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-3.77011</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-73.26394999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>608</v>
-      </c>
-      <c r="J5" t="n">
-        <v>26</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-3.77011</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-73.26395</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>708 ARBOLITO DEL SABER</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-3.77388</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-73.2653</v>
-      </c>
-      <c r="I6" t="n">
-        <v>268</v>
-      </c>
-      <c r="J6" t="n">
-        <v>11</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-3.77388</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-73.2653</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>60014 SANTO CRISTO BAGAZAN / 757 SANTO CRISTO DE BAGAZAN</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-3.76185</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-73.25154000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="J7" t="n">
-        <v>91</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-3.76185</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-73.25154</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>60010 VALENTIN PANIAGUA CORAZAO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-3.76272</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-73.2533</v>
-      </c>
-      <c r="I8" t="n">
-        <v>256</v>
-      </c>
-      <c r="J8" t="n">
-        <v>16</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-3.76272</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-73.2533</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>60022 JUAN DIEGO NATAL</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-3.76207</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-73.24668</v>
-      </c>
-      <c r="I9" t="n">
-        <v>340</v>
-      </c>
-      <c r="J9" t="n">
-        <v>22</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-3.76207</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-73.24668</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>60025</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-3.733295</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-73.23141699999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>222</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-3.733295</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-73.231417</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>60026 RUY GUZMAN HIDALGO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-3.76574</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-73.26163</v>
-      </c>
-      <c r="I11" t="n">
-        <v>917</v>
-      </c>
-      <c r="J11" t="n">
-        <v>39</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-3.76574</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-73.26163</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>60138</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-3.76446</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-73.24883</v>
-      </c>
-      <c r="I12" t="n">
-        <v>349</v>
-      </c>
-      <c r="J12" t="n">
-        <v>18</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-3.76446</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-73.24883</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>60192</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-3.76899</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-73.26224999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>759</v>
-      </c>
-      <c r="J13" t="n">
-        <v>41</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-3.76899</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-73.26225</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>60743 ENRY HERVE LINARES SOTO</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-3.76775</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-73.25802</v>
-      </c>
-      <c r="I14" t="n">
-        <v>600</v>
-      </c>
-      <c r="J14" t="n">
-        <v>31</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-3.76775</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-73.25802</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>60993 RAMON CASTILLA / 60993 RAMON CASTILLA Y MARQUEZADO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-3.7709</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-73.27341</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2947</v>
-      </c>
-      <c r="J15" t="n">
-        <v>131</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-3.7709</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-73.27341</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2947</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>601051</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-3.76392</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-73.24917000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>353</v>
-      </c>
-      <c r="J16" t="n">
-        <v>22</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-3.76392</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-73.24917</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>601534 SAN LUCAS</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-3.775</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-73.26645000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>774</v>
-      </c>
-      <c r="J17" t="n">
-        <v>36</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-3.775</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-73.26645</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>SAGRADA FAMILIA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-3.772829</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-73.272949</v>
-      </c>
-      <c r="I18" t="n">
-        <v>925</v>
-      </c>
-      <c r="J18" t="n">
-        <v>45</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-3.772829</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-73.272949</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-3.759941</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-73.24969299999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>871</v>
-      </c>
-      <c r="J19" t="n">
-        <v>52</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-3.759941</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-73.249693</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LORETO-MAYNAS-BELEN.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-BELEN.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>365014</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61006 SARA ALICIA SABERBEIN PINEDO</t>
+          <t>708 ARBOLITO DEL SABER</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.76143</t>
+          <t>-3.77388</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-73.24947</t>
+          <t>-73.2653</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>364057</t>
+          <t>365995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>159 NIÑO DE JESUS DE PRAGA</t>
+          <t>60993 RAMON CASTILLA / 60993 RAMON CASTILLA Y MARQUEZADO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.75938</t>
+          <t>-3.7709</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-73.25171</t>
+          <t>-73.27341</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>131</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>364123</t>
+          <t>365207</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>178 LILY VASQUEZ RIBEIRO</t>
+          <t>60025</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.76196</t>
+          <t>-3.733295</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-73.25253</t>
+          <t>-73.231417</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>364378</t>
+          <t>365132</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>397 CORAZON DE JESUS</t>
+          <t>60010 VALENTIN PANIAGUA CORAZAO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.77011</t>
+          <t>-3.76272</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-73.26395</t>
+          <t>-73.2533</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>256</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>365014</t>
+          <t>365660</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>708 ARBOLITO DEL SABER</t>
+          <t>60138</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.77388</t>
+          <t>-3.76446</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-73.2653</t>
+          <t>-73.24883</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>349</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>365071</t>
+          <t>364057</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60014 SANTO CRISTO BAGAZAN / 757 SANTO CRISTO DE BAGAZAN</t>
+          <t>159 NIÑO DE JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.76185</t>
+          <t>-3.75938</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-73.25154</t>
+          <t>-73.25171</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>415</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>365132</t>
+          <t>365170</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60010 VALENTIN PANIAGUA CORAZAO</t>
+          <t>60022 JUAN DIEGO NATAL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.76272</t>
+          <t>-3.76207</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-73.2533</t>
+          <t>-73.24668</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,27 +935,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>365170</t>
+          <t>366122</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60022 JUAN DIEGO NATAL</t>
+          <t>601051</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.76207</t>
+          <t>-3.76392</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-73.24668</t>
+          <t>-73.24917</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>365207</t>
+          <t>364123</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60025</t>
+          <t>178 LILY VASQUEZ RIBEIRO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.733295</t>
+          <t>-3.76196</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-73.231417</t>
+          <t>-73.25253</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>387</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>365212</t>
+          <t>364378</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60026 RUY GUZMAN HIDALGO</t>
+          <t>397 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.76574</t>
+          <t>-3.77011</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-73.26163</t>
+          <t>-73.26395</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>608</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>365660</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60138</t>
+          <t>61006 SARA ALICIA SABERBEIN PINEDO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.76446</t>
+          <t>-3.76143</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-73.24883</t>
+          <t>-73.24947</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>518</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>365702</t>
+          <t>365759</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60192</t>
+          <t>60743 ENRY HERVE LINARES SOTO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.76899</t>
+          <t>-3.76775</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-73.26225</t>
+          <t>-73.25802</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>365759</t>
+          <t>366612</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60743 ENRY HERVE LINARES SOTO</t>
+          <t>601534 SAN LUCAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.76775</t>
+          <t>-3.775</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-73.25802</t>
+          <t>-73.26645</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>774</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>365995</t>
+          <t>365212</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60993 RAMON CASTILLA / 60993 RAMON CASTILLA Y MARQUEZADO</t>
+          <t>60026 RUY GUZMAN HIDALGO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.7709</t>
+          <t>-3.76574</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-73.27341</t>
+          <t>-73.26163</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>917</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>366122</t>
+          <t>365702</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>601051</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.76392</t>
+          <t>-3.76899</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-73.24917</t>
+          <t>-73.26225</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>759</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>366612</t>
+          <t>367188</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>601534 SAN LUCAS</t>
+          <t>SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.775</t>
+          <t>-3.772829</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-73.26645</t>
+          <t>-73.272949</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>925</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>367188</t>
+          <t>367503</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SAGRADA FAMILIA</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.772829</t>
+          <t>-3.759941</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-73.272949</t>
+          <t>-73.249693</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>871</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>367503</t>
+          <t>365071</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>60014 SANTO CRISTO BAGAZAN / 757 SANTO CRISTO DE BAGAZAN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.759941</t>
+          <t>-3.76185</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-73.249693</t>
+          <t>-73.25154</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">

--- a/ZonasEscolares/excels/LORETO-MAYNAS-BELEN.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-BELEN.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>365014</t>
+          <t>367503</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>708 ARBOLITO DEL SABER</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.77388</t>
+          <t>871</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-73.2653</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-3.759941</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-73.249693</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>365995</t>
+          <t>367188</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60993 RAMON CASTILLA / 60993 RAMON CASTILLA Y MARQUEZADO</t>
+          <t>SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.7709</t>
+          <t>925</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-73.27341</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>-3.772829</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>-73.272949</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>365207</t>
+          <t>366612</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60025</t>
+          <t>601534 SAN LUCAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.733295</t>
+          <t>774</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-73.231417</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-3.775</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-73.26645</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>365132</t>
+          <t>366122</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60010 VALENTIN PANIAGUA CORAZAO</t>
+          <t>601051</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.76272</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-73.2533</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>-3.76392</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-73.24917</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>365660</t>
+          <t>365995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60138</t>
+          <t>60993 RAMON CASTILLA / 60993 RAMON CASTILLA Y MARQUEZADO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.76446</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-73.24883</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>-3.7709</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-73.27341</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>364057</t>
+          <t>365759</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>159 NIÑO DE JESUS DE PRAGA</t>
+          <t>60743 ENRY HERVE LINARES SOTO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.75938</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-73.25171</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>-3.76775</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-73.25802</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>365170</t>
+          <t>365702</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60022 JUAN DIEGO NATAL</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.76207</t>
+          <t>759</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-73.24668</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>-3.76899</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-73.26225</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>366122</t>
+          <t>365660</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>601051</t>
+          <t>60138</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.76392</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-73.24917</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>-3.76446</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-73.24883</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>364123</t>
+          <t>365212</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>178 LILY VASQUEZ RIBEIRO</t>
+          <t>60026 RUY GUZMAN HIDALGO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.76196</t>
+          <t>917</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-73.25253</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>-3.76574</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-73.26163</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>364378</t>
+          <t>365207</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>397 CORAZON DE JESUS</t>
+          <t>60025</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.77011</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-73.26395</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>-3.733295</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-73.231417</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>365170</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61006 SARA ALICIA SABERBEIN PINEDO</t>
+          <t>60022 JUAN DIEGO NATAL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.76143</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-73.24947</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>-3.76207</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-73.24668</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>365759</t>
+          <t>365132</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60743 ENRY HERVE LINARES SOTO</t>
+          <t>60010 VALENTIN PANIAGUA CORAZAO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.76775</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-73.25802</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-3.76272</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-73.2533</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>366612</t>
+          <t>365071</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>601534 SAN LUCAS</t>
+          <t>60014 SANTO CRISTO BAGAZAN / 757 SANTO CRISTO DE BAGAZAN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.775</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-73.26645</t>
+          <t>91</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>-3.76185</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-73.25154</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>365212</t>
+          <t>365014</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60026 RUY GUZMAN HIDALGO</t>
+          <t>708 ARBOLITO DEL SABER</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.76574</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-73.26163</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>-3.77388</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-73.2653</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>365702</t>
+          <t>364378</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60192</t>
+          <t>397 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.76899</t>
+          <t>608</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-73.26225</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>-3.77011</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-73.26395</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>367188</t>
+          <t>364123</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SAGRADA FAMILIA</t>
+          <t>178 LILY VASQUEZ RIBEIRO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.772829</t>
+          <t>387</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-73.272949</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>-3.76196</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-73.25253</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>367503</t>
+          <t>364057</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>159 NIÑO DE JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.759941</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-73.249693</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>-3.75938</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-73.25171</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>365071</t>
+          <t>002061</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60014 SANTO CRISTO BAGAZAN / 757 SANTO CRISTO DE BAGAZAN</t>
+          <t>61006 SARA ALICIA SABERBEIN PINEDO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.76185</t>
+          <t>518</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-73.25154</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>-3.76143</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-73.24947</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">

--- a/ZonasEscolares/excels/LORETO-MAYNAS-BELEN.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-BELEN.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
